--- a/conference_registration_forms/017_internal_audit_conference_registration--conference_registration_forms.xlsx
+++ b/conference_registration_forms/017_internal_audit_conference_registration--conference_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>session_1</t>
+          <t>session_1_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Session 1 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>session_2</t>
+          <t>session_2_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Session 2 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>session_3</t>
+          <t>session_3_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Session 3</t>
+          <t>Session 3 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>session_1</t>
+          <t>session_1_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Session 1</t>
+          <t>Session 1 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>session_2</t>
+          <t>session_2_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Session 2</t>
+          <t>Session 2 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>session_3</t>
+          <t>session_3_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Session 3</t>
+          <t>Session 3 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1424,8 +1424,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'session_1'}</t>
+          <t>session_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Session 1'}</t>
+          <t>Session 1</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'session_2'}</t>
+          <t>session_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Session 2'}</t>
+          <t>Session 2</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'session_3'}</t>
+          <t>session_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Session 3'}</t>
+          <t>Session 3</t>
         </is>
       </c>
     </row>
